--- a/05_성장팀/팀챌린지_향상점수계산.xlsx
+++ b/05_성장팀/팀챌린지_향상점수계산.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="144">
   <si>
     <r>
       <rPr>
@@ -2558,6 +2558,334 @@
     <r>
       <rPr>
         <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검증 기록 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-11-01] </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 규칙을 파이썬으로 따로 계산해 대조</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확정값 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노란 칸 변경 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가지 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가지 경우 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 195</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 항목 모두 일치</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오류 셀 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(±20%p </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정확한 경계 포함</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자세한 내용</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 05_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성장팀</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/2026-11-01_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">팀챌린지</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설문과합격기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md '</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">엑셀 검증 기록</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="13"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
@@ -8421,7 +8749,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8490,6 +8818,21 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -8586,7 +8929,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8655,6 +8998,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8663,7 +9010,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8737,7 +9084,7 @@
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF375623"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -26120,327 +26467,332 @@
         <v>79</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="B6" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="20" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="B7" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="20" t="n">
         <v>-20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="B8" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="20" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="B9" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="B10" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="20" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="B11" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="20" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="B12" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="20" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="B13" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="20" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="18" t="s">
+      <c r="A14" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="B14" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="18" t="s">
+      <c r="A15" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="B15" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="20" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="18" t="s">
+      <c r="A16" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="B16" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="20" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="18" t="s">
+      <c r="A17" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="B17" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="20" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/05_성장팀/팀챌린지_향상점수계산.xlsx
+++ b/05_성장팀/팀챌린지_향상점수계산.xlsx
@@ -23571,7 +23571,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>붙여넣기 방법 (Socrative 또는 우리 웹앱 CSV)</t>
+          <t>붙여넣기 방법 (Socrative)</t>
         </is>
       </c>
     </row>
@@ -23592,7 +23592,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>우리 웹앱(트랙 B): 내보내기 CSV 열 순서를 '참가자코드, 맞힌 수, 문항 수'로 맞추면 R열에 그대로 붙여넣을 수 있습니다. 코드 앞뒤 빈칸·대소문자는 자동으로 정리됩니다.</t>
+          <t>(참고) 웹앱 v0.3에는 결과 저장·CSV가 없습니다. v0.4를 만들면 CSV 열 순서를 '참가자코드, 맞힌 수, 문항 수'로 맞춰 R열에 붙여넣습니다.</t>
         </is>
       </c>
     </row>
